--- a/Daily_Report/Top 7 broker List with its Turnover 2024-11-17.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-11-17.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="272">
   <si>
     <t>Date: 2024-11-17</t>
   </si>
@@ -62,106 +62,106 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
+    <t>Linch Stock Market Limited</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Nepal Stock House Pvt. Limited</t>
-  </si>
-  <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Sani Securities Company Limited</t>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
     <t>34</t>
   </si>
   <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>49</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>1,303,288,379.15</t>
-  </si>
-  <si>
-    <t>1,093,452,187.5</t>
-  </si>
-  <si>
-    <t>1,049,466,461.0</t>
-  </si>
-  <si>
-    <t>1,045,855,711.6</t>
-  </si>
-  <si>
-    <t>819,941,454.9</t>
-  </si>
-  <si>
-    <t>792,304,983.3</t>
-  </si>
-  <si>
-    <t>733,242,157.94</t>
-  </si>
-  <si>
-    <t>521,869,119.25</t>
-  </si>
-  <si>
-    <t>457,878,706.4</t>
-  </si>
-  <si>
-    <t>697,985,104.62</t>
-  </si>
-  <si>
-    <t>214,025,376.5</t>
-  </si>
-  <si>
-    <t>516,591,119.3</t>
-  </si>
-  <si>
-    <t>231,629,419.8</t>
-  </si>
-  <si>
-    <t>323,736,204.2</t>
-  </si>
-  <si>
-    <t>781,419,259.9</t>
-  </si>
-  <si>
-    <t>635,573,481.1</t>
-  </si>
-  <si>
-    <t>351,481,356.38</t>
-  </si>
-  <si>
-    <t>831,830,335.1</t>
-  </si>
-  <si>
-    <t>303,350,335.6</t>
-  </si>
-  <si>
-    <t>560,675,563.5</t>
-  </si>
-  <si>
-    <t>409,505,953.74</t>
+    <t>57</t>
+  </si>
+  <si>
+    <t>1,299,691,318.55</t>
+  </si>
+  <si>
+    <t>1,019,145,306.9</t>
+  </si>
+  <si>
+    <t>873,684,777.0</t>
+  </si>
+  <si>
+    <t>838,499,276.0</t>
+  </si>
+  <si>
+    <t>837,122,606.49</t>
+  </si>
+  <si>
+    <t>768,681,464.4</t>
+  </si>
+  <si>
+    <t>661,232,620.23</t>
+  </si>
+  <si>
+    <t>656,826,559.04</t>
+  </si>
+  <si>
+    <t>414,335,822.0</t>
+  </si>
+  <si>
+    <t>476,911,752.1</t>
+  </si>
+  <si>
+    <t>409,211,564.7</t>
+  </si>
+  <si>
+    <t>433,766,742.85</t>
+  </si>
+  <si>
+    <t>429,936,904.92</t>
+  </si>
+  <si>
+    <t>358,722,820.7</t>
+  </si>
+  <si>
+    <t>642,864,759.5</t>
+  </si>
+  <si>
+    <t>604,809,484.9</t>
+  </si>
+  <si>
+    <t>396,773,024.9</t>
+  </si>
+  <si>
+    <t>429,287,711.3</t>
+  </si>
+  <si>
+    <t>403,355,863.64</t>
+  </si>
+  <si>
+    <t>338,744,559.48</t>
+  </si>
+  <si>
+    <t>302,509,799.52</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,361 +179,319 @@
     <t>% of turnover</t>
   </si>
   <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>171,486,448.4</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>36,269,658.1</t>
+  </si>
+  <si>
+    <t>FMDBL</t>
+  </si>
+  <si>
+    <t>30,210,108.0</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>22,789,470.8</t>
+  </si>
+  <si>
+    <t>ANLB</t>
+  </si>
+  <si>
+    <t>22,595,415.0</t>
+  </si>
+  <si>
+    <t>134,527,366.6</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>68,224,791.7</t>
+  </si>
+  <si>
+    <t>39,584,679.0</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>7,634,543.1</t>
+  </si>
+  <si>
+    <t>NICL</t>
+  </si>
+  <si>
+    <t>5,067,695.0</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>80,543,518.7</t>
+  </si>
+  <si>
+    <t>16,094,973.5</t>
+  </si>
+  <si>
+    <t>HURJA</t>
+  </si>
+  <si>
+    <t>14,631,746.4</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>13,854,806.4</t>
+  </si>
+  <si>
+    <t>SHEL</t>
+  </si>
+  <si>
+    <t>12,558,266.4</t>
+  </si>
+  <si>
+    <t>PFL</t>
+  </si>
+  <si>
+    <t>26,442,980.1</t>
+  </si>
+  <si>
+    <t>15,328,268.1</t>
+  </si>
+  <si>
+    <t>12,371,301.8</t>
+  </si>
+  <si>
+    <t>ALICL</t>
+  </si>
+  <si>
+    <t>8,040,412.0</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>7,234,480.7</t>
+  </si>
+  <si>
+    <t>18,002,342.2</t>
+  </si>
+  <si>
+    <t>17,511,902.89</t>
+  </si>
+  <si>
+    <t>16,433,736.7</t>
+  </si>
+  <si>
+    <t>15,204,065.0</t>
+  </si>
+  <si>
+    <t>GMFIL</t>
+  </si>
+  <si>
+    <t>13,867,000.0</t>
+  </si>
+  <si>
+    <t>15,840,409.8</t>
+  </si>
+  <si>
+    <t>12,804,694.0</t>
+  </si>
+  <si>
+    <t>11,776,578.4</t>
+  </si>
+  <si>
+    <t>MNBBL</t>
+  </si>
+  <si>
+    <t>11,608,405.1</t>
+  </si>
+  <si>
+    <t>HPPL</t>
+  </si>
+  <si>
+    <t>10,739,712.3</t>
+  </si>
+  <si>
+    <t>27,532,750.4</t>
+  </si>
+  <si>
+    <t>18,499,813.0</t>
+  </si>
+  <si>
+    <t>14,706,744.2</t>
+  </si>
+  <si>
     <t>BFC</t>
   </si>
   <si>
-    <t>107,428,735.5</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>80,293,944.59</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>58,617,233.7</t>
-  </si>
-  <si>
-    <t>BPCL</t>
-  </si>
-  <si>
-    <t>28,388,187.8</t>
-  </si>
-  <si>
-    <t>MEL</t>
-  </si>
-  <si>
-    <t>19,475,383.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>71,761,740.3</t>
+    <t>10,702,004.19</t>
+  </si>
+  <si>
+    <t>8,469,865.4</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>142,981,879.3</t>
+  </si>
+  <si>
+    <t>NTC</t>
+  </si>
+  <si>
+    <t>27,451,221.5</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>26,168,250.5</t>
+  </si>
+  <si>
+    <t>15,907,538.4</t>
+  </si>
+  <si>
+    <t>14,340,560.6</t>
+  </si>
+  <si>
+    <t>171,577,160.1</t>
+  </si>
+  <si>
+    <t>96,569,061.8</t>
+  </si>
+  <si>
+    <t>89,990,996.0</t>
+  </si>
+  <si>
+    <t>31,158,071.0</t>
+  </si>
+  <si>
+    <t>PHCL</t>
+  </si>
+  <si>
+    <t>27,481,976.2</t>
+  </si>
+  <si>
+    <t>45,912,248.1</t>
+  </si>
+  <si>
+    <t>7,582,701.5</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>7,299,106.9</t>
+  </si>
+  <si>
+    <t>SPDL</t>
+  </si>
+  <si>
+    <t>6,559,699.8</t>
+  </si>
+  <si>
+    <t>6,555,803.3</t>
+  </si>
+  <si>
+    <t>14,487,738.2</t>
+  </si>
+  <si>
+    <t>CGH</t>
+  </si>
+  <si>
+    <t>14,107,960.8</t>
+  </si>
+  <si>
+    <t>GBLBS</t>
+  </si>
+  <si>
+    <t>13,085,739.5</t>
+  </si>
+  <si>
+    <t>8,585,420.3</t>
+  </si>
+  <si>
+    <t>8,054,000.2</t>
+  </si>
+  <si>
+    <t>34,290,233.2</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>14,794,872.4</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>12,785,057.0</t>
+  </si>
+  <si>
+    <t>11,446,124.4</t>
+  </si>
+  <si>
+    <t>USHEC</t>
+  </si>
+  <si>
+    <t>10,740,237.5</t>
+  </si>
+  <si>
+    <t>MAKAR</t>
+  </si>
+  <si>
+    <t>14,982,979.0</t>
+  </si>
+  <si>
+    <t>12,319,751.4</t>
+  </si>
+  <si>
+    <t>11,411,859.5</t>
+  </si>
+  <si>
+    <t>ADBL</t>
+  </si>
+  <si>
+    <t>9,353,647.69</t>
   </si>
   <si>
     <t>HIDCLP</t>
   </si>
   <si>
-    <t>44,041,460.0</t>
-  </si>
-  <si>
-    <t>PCBL</t>
-  </si>
-  <si>
-    <t>43,914,521.0</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>25,602,436.1</t>
-  </si>
-  <si>
-    <t>GLH</t>
-  </si>
-  <si>
-    <t>24,991,805.0</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>147,794,892.0</t>
-  </si>
-  <si>
-    <t>MNBBL</t>
-  </si>
-  <si>
-    <t>126,452,042.4</t>
-  </si>
-  <si>
-    <t>SHEL</t>
-  </si>
-  <si>
-    <t>101,015,601.3</t>
-  </si>
-  <si>
-    <t>KSBBL</t>
-  </si>
-  <si>
-    <t>40,818,732.2</t>
-  </si>
-  <si>
-    <t>19,001,194.6</t>
-  </si>
-  <si>
-    <t>MCHL</t>
-  </si>
-  <si>
-    <t>27,714,459.2</t>
-  </si>
-  <si>
-    <t>HPPL</t>
-  </si>
-  <si>
-    <t>26,198,093.5</t>
-  </si>
-  <si>
-    <t>RFPL</t>
-  </si>
-  <si>
-    <t>20,669,490.2</t>
-  </si>
-  <si>
-    <t>NICL</t>
-  </si>
-  <si>
-    <t>15,829,798.0</t>
-  </si>
-  <si>
-    <t>14,583,450.0</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>108,137,297.2</t>
-  </si>
-  <si>
-    <t>CLI</t>
-  </si>
-  <si>
-    <t>85,036,968.0</t>
-  </si>
-  <si>
-    <t>TPC</t>
-  </si>
-  <si>
-    <t>66,727,884.0</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>16,030,240.6</t>
-  </si>
-  <si>
-    <t>NRM</t>
-  </si>
-  <si>
-    <t>15,226,934.0</t>
-  </si>
-  <si>
-    <t>NICA</t>
-  </si>
-  <si>
-    <t>23,569,940.0</t>
-  </si>
-  <si>
-    <t>SFCL</t>
-  </si>
-  <si>
-    <t>19,276,057.5</t>
-  </si>
-  <si>
-    <t>GLBSL</t>
-  </si>
-  <si>
-    <t>12,391,091.9</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>11,876,348.8</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>9,353,347.4</t>
-  </si>
-  <si>
-    <t>SLBSL</t>
-  </si>
-  <si>
-    <t>38,837,862.0</t>
-  </si>
-  <si>
-    <t>HLBSL</t>
-  </si>
-  <si>
-    <t>13,723,611.0</t>
-  </si>
-  <si>
-    <t>12,232,252.0</t>
-  </si>
-  <si>
-    <t>GMFIL</t>
-  </si>
-  <si>
-    <t>11,201,710.0</t>
-  </si>
-  <si>
-    <t>MPFL</t>
-  </si>
-  <si>
-    <t>11,008,105.5</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>252,260,955.2</t>
-  </si>
-  <si>
-    <t>208,223,293.7</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>27,873,740.0</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>26,076,150.5</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>22,430,841.5</t>
-  </si>
-  <si>
-    <t>372,946,366.3</t>
-  </si>
-  <si>
-    <t>MMKJL</t>
-  </si>
-  <si>
-    <t>37,829,896.0</t>
-  </si>
-  <si>
-    <t>31,816,180.6</t>
-  </si>
-  <si>
-    <t>8,249,988.2</t>
-  </si>
-  <si>
-    <t>NADEP</t>
-  </si>
-  <si>
-    <t>6,159,676.3</t>
-  </si>
-  <si>
-    <t>68,813,429.59</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>55,647,435.1</t>
-  </si>
-  <si>
-    <t>28,597,338.4</t>
-  </si>
-  <si>
-    <t>16,320,021.0</t>
-  </si>
-  <si>
-    <t>MAKAR</t>
-  </si>
-  <si>
-    <t>14,896,939.0</t>
-  </si>
-  <si>
-    <t>645,285,791.1</t>
-  </si>
-  <si>
-    <t>SHLB</t>
-  </si>
-  <si>
-    <t>68,078,966.0</t>
-  </si>
-  <si>
-    <t>GBLBS</t>
-  </si>
-  <si>
-    <t>15,694,715.0</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>11,236,835.8</t>
-  </si>
-  <si>
-    <t>CYCL</t>
-  </si>
-  <si>
-    <t>5,627,729.4</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>36,386,390.9</t>
-  </si>
-  <si>
-    <t>25,197,245.4</t>
-  </si>
-  <si>
-    <t>15,506,774.2</t>
-  </si>
-  <si>
-    <t>12,033,775.0</t>
-  </si>
-  <si>
-    <t>MMF1</t>
-  </si>
-  <si>
-    <t>7,191,646.0</t>
-  </si>
-  <si>
-    <t>190,719,797.1</t>
-  </si>
-  <si>
-    <t>78,473,462.5</t>
-  </si>
-  <si>
-    <t>65,374,789.7</t>
-  </si>
-  <si>
-    <t>41,338,013.29</t>
-  </si>
-  <si>
-    <t>24,645,142.5</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>172,778,014.2</t>
-  </si>
-  <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>53,397,382.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>16,244,330.8</t>
-  </si>
-  <si>
-    <t>6,846,117.7</t>
-  </si>
-  <si>
-    <t>5,826,503.0</t>
+    <t>7,447,680.2</t>
+  </si>
+  <si>
+    <t>SMH</t>
+  </si>
+  <si>
+    <t>13,212,607.0</t>
+  </si>
+  <si>
+    <t>12,326,155.5</t>
+  </si>
+  <si>
+    <t>11,567,220.6</t>
+  </si>
+  <si>
+    <t>MBL</t>
+  </si>
+  <si>
+    <t>9,605,626.1</t>
+  </si>
+  <si>
+    <t>7,621,788.8</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -551,109 +509,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>692,140,852.3</t>
-  </si>
-  <si>
-    <t>484,322,213.5</t>
-  </si>
-  <si>
-    <t>458,120,582.2</t>
-  </si>
-  <si>
-    <t>380,728,794.7</t>
-  </si>
-  <si>
-    <t>343,804,306.8</t>
+    <t>451,710,372.7</t>
+  </si>
+  <si>
+    <t>418,287,007.4</t>
+  </si>
+  <si>
+    <t>354,098,888.8</t>
+  </si>
+  <si>
+    <t>340,037,643.1</t>
+  </si>
+  <si>
+    <t>231,566,433.3</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>3,116,380,409.8</t>
+    <t>3,587,441,164.6</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>2,701,299,588.4</t>
+    <t>2,546,162,782.19</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,662,427,471.7</t>
+    <t>2,068,357,876.4</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>1,104,470,485.3</t>
+  </si>
+  <si>
+    <t>Development Banks</t>
+  </si>
+  <si>
+    <t>786,272,606.0</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>1,020,460,233.2</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>881,653,504.9</t>
-  </si>
-  <si>
-    <t>Development Banks</t>
-  </si>
-  <si>
-    <t>721,509,977.5</t>
+    <t>483,066,017.3</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>262,865,418.0</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>261,323,659.6</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>577,217,630.29</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>296,934,202.0</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>233,077,137.0</t>
+    <t>217,121,361.5</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>116,806,538.3</t>
+    <t>161,603,756.8</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>101,635,633.0</t>
+    <t>105,225,715.3</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>100,671,283.8</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>86,969,061.67</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>72,083,874.7</t>
+    <t>25,075,507.81</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>10,721,292.0</t>
+    <t>13,674,522.0</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>798,843.0</t>
+    <t>3,424,748.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -665,214 +623,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>198,124,022.9</t>
-  </si>
-  <si>
-    <t>180,229,074.1</t>
-  </si>
-  <si>
-    <t>71,658,232.5</t>
-  </si>
-  <si>
-    <t>26,345,377.6</t>
-  </si>
-  <si>
-    <t>16,212,084.7</t>
-  </si>
-  <si>
-    <t>125,938,062.1</t>
-  </si>
-  <si>
-    <t>99,125,560.5</t>
-  </si>
-  <si>
-    <t>75,835,778.2</t>
-  </si>
-  <si>
-    <t>50,533,478.4</t>
-  </si>
-  <si>
-    <t>46,021,681.8</t>
-  </si>
-  <si>
-    <t>323,553,217.2</t>
-  </si>
-  <si>
-    <t>178,562,102.9</t>
-  </si>
-  <si>
-    <t>63,940,524.8</t>
-  </si>
-  <si>
-    <t>47,149,654.2</t>
-  </si>
-  <si>
-    <t>24,880,322.3</t>
-  </si>
-  <si>
-    <t>73,564,425.4</t>
-  </si>
-  <si>
-    <t>45,568,285.5</t>
-  </si>
-  <si>
-    <t>34,134,209.5</t>
-  </si>
-  <si>
-    <t>23,566,727.5</t>
-  </si>
-  <si>
-    <t>16,694,166.0</t>
-  </si>
-  <si>
-    <t>244,018,921.0</t>
-  </si>
-  <si>
-    <t>134,728,889.0</t>
-  </si>
-  <si>
-    <t>42,762,884.9</t>
-  </si>
-  <si>
-    <t>30,124,149.2</t>
-  </si>
-  <si>
-    <t>27,959,598.0</t>
-  </si>
-  <si>
-    <t>50,804,086.2</t>
-  </si>
-  <si>
-    <t>44,015,647.1</t>
-  </si>
-  <si>
-    <t>38,882,863.6</t>
-  </si>
-  <si>
-    <t>34,798,029.2</t>
-  </si>
-  <si>
-    <t>27,436,475.1</t>
-  </si>
-  <si>
-    <t>69,957,398.7</t>
-  </si>
-  <si>
-    <t>64,690,058.9</t>
-  </si>
-  <si>
-    <t>62,279,378.1</t>
-  </si>
-  <si>
-    <t>57,940,330.9</t>
-  </si>
-  <si>
-    <t>17,018,042.0</t>
-  </si>
-  <si>
-    <t>554,480,011.0</t>
-  </si>
-  <si>
-    <t>69,214,211.59</t>
-  </si>
-  <si>
-    <t>46,288,142.0</t>
-  </si>
-  <si>
-    <t>28,584,365.8</t>
-  </si>
-  <si>
-    <t>23,353,868.1</t>
-  </si>
-  <si>
-    <t>376,098,540.1</t>
-  </si>
-  <si>
-    <t>85,381,183.5</t>
-  </si>
-  <si>
-    <t>57,343,402.0</t>
-  </si>
-  <si>
-    <t>53,730,434.7</t>
-  </si>
-  <si>
-    <t>22,177,993.8</t>
-  </si>
-  <si>
-    <t>137,809,958.69</t>
-  </si>
-  <si>
-    <t>56,375,644.3</t>
-  </si>
-  <si>
-    <t>41,885,174.4</t>
-  </si>
-  <si>
-    <t>41,846,489.4</t>
-  </si>
-  <si>
-    <t>21,935,449.6</t>
-  </si>
-  <si>
-    <t>667,563,319.9</t>
-  </si>
-  <si>
-    <t>96,823,508.5</t>
-  </si>
-  <si>
-    <t>26,448,722.6</t>
-  </si>
-  <si>
-    <t>16,563,338.4</t>
-  </si>
-  <si>
-    <t>10,532,429.69</t>
-  </si>
-  <si>
-    <t>97,084,600.2</t>
-  </si>
-  <si>
-    <t>68,010,643.8</t>
-  </si>
-  <si>
-    <t>63,182,416.5</t>
-  </si>
-  <si>
-    <t>19,643,165.89</t>
-  </si>
-  <si>
-    <t>14,920,081.2</t>
-  </si>
-  <si>
-    <t>192,911,320.6</t>
-  </si>
-  <si>
-    <t>113,700,834.7</t>
-  </si>
-  <si>
-    <t>95,256,238.0</t>
-  </si>
-  <si>
-    <t>84,991,232.5</t>
-  </si>
-  <si>
-    <t>50,149,418.2</t>
-  </si>
-  <si>
-    <t>173,894,870.0</t>
-  </si>
-  <si>
-    <t>58,737,838.0</t>
-  </si>
-  <si>
-    <t>41,863,125.79</t>
-  </si>
-  <si>
-    <t>36,822,075.2</t>
-  </si>
-  <si>
-    <t>30,052,657.9</t>
+    <t>286,454,828.0</t>
+  </si>
+  <si>
+    <t>102,810,028.6</t>
+  </si>
+  <si>
+    <t>97,906,353.5</t>
+  </si>
+  <si>
+    <t>65,212,927.8</t>
+  </si>
+  <si>
+    <t>27,657,371.1</t>
+  </si>
+  <si>
+    <t>267,540,594.3</t>
+  </si>
+  <si>
+    <t>52,752,595.2</t>
+  </si>
+  <si>
+    <t>41,447,187.79</t>
+  </si>
+  <si>
+    <t>18,510,720.1</t>
+  </si>
+  <si>
+    <t>8,300,207.1</t>
+  </si>
+  <si>
+    <t>156,245,873.4</t>
+  </si>
+  <si>
+    <t>132,440,346.4</t>
+  </si>
+  <si>
+    <t>57,586,654.4</t>
+  </si>
+  <si>
+    <t>52,956,568.7</t>
+  </si>
+  <si>
+    <t>25,828,573.6</t>
+  </si>
+  <si>
+    <t>113,043,510.8</t>
+  </si>
+  <si>
+    <t>83,307,432.0</t>
+  </si>
+  <si>
+    <t>75,662,616.8</t>
+  </si>
+  <si>
+    <t>37,144,597.4</t>
+  </si>
+  <si>
+    <t>25,730,845.9</t>
+  </si>
+  <si>
+    <t>123,203,514.9</t>
+  </si>
+  <si>
+    <t>87,982,861.9</t>
+  </si>
+  <si>
+    <t>75,663,224.3</t>
+  </si>
+  <si>
+    <t>56,017,206.1</t>
+  </si>
+  <si>
+    <t>29,090,769.0</t>
+  </si>
+  <si>
+    <t>122,080,284.7</t>
+  </si>
+  <si>
+    <t>91,542,100.9</t>
+  </si>
+  <si>
+    <t>76,953,719.9</t>
+  </si>
+  <si>
+    <t>44,063,470.5</t>
+  </si>
+  <si>
+    <t>33,554,649.9</t>
+  </si>
+  <si>
+    <t>107,975,268.8</t>
+  </si>
+  <si>
+    <t>90,583,683.0</t>
+  </si>
+  <si>
+    <t>61,602,472.0</t>
+  </si>
+  <si>
+    <t>32,671,179.8</t>
+  </si>
+  <si>
+    <t>24,690,249.4</t>
+  </si>
+  <si>
+    <t>281,656,362.2</t>
+  </si>
+  <si>
+    <t>95,286,226.7</t>
+  </si>
+  <si>
+    <t>84,606,942.2</t>
+  </si>
+  <si>
+    <t>45,906,441.8</t>
+  </si>
+  <si>
+    <t>30,307,120.1</t>
+  </si>
+  <si>
+    <t>314,354,665.8</t>
+  </si>
+  <si>
+    <t>166,242,321.19</t>
+  </si>
+  <si>
+    <t>39,936,813.4</t>
+  </si>
+  <si>
+    <t>24,910,559.4</t>
+  </si>
+  <si>
+    <t>19,712,071.2</t>
+  </si>
+  <si>
+    <t>117,834,752.6</t>
+  </si>
+  <si>
+    <t>113,945,321.4</t>
+  </si>
+  <si>
+    <t>52,426,443.8</t>
+  </si>
+  <si>
+    <t>38,749,955.9</t>
+  </si>
+  <si>
+    <t>24,419,316.3</t>
+  </si>
+  <si>
+    <t>123,251,415.3</t>
+  </si>
+  <si>
+    <t>93,303,686.3</t>
+  </si>
+  <si>
+    <t>56,947,167.1</t>
+  </si>
+  <si>
+    <t>52,788,879.1</t>
+  </si>
+  <si>
+    <t>22,242,444.1</t>
+  </si>
+  <si>
+    <t>95,339,852.3</t>
+  </si>
+  <si>
+    <t>82,813,761.3</t>
+  </si>
+  <si>
+    <t>68,154,094.4</t>
+  </si>
+  <si>
+    <t>51,753,282.1</t>
+  </si>
+  <si>
+    <t>30,621,782.5</t>
+  </si>
+  <si>
+    <t>90,733,791.7</t>
+  </si>
+  <si>
+    <t>85,261,492.0</t>
+  </si>
+  <si>
+    <t>44,412,587.8</t>
+  </si>
+  <si>
+    <t>34,485,570.6</t>
+  </si>
+  <si>
+    <t>29,353,118.3</t>
+  </si>
+  <si>
+    <t>91,185,904.0</t>
+  </si>
+  <si>
+    <t>63,323,783.6</t>
+  </si>
+  <si>
+    <t>62,348,015.1</t>
+  </si>
+  <si>
+    <t>30,466,043.0</t>
+  </si>
+  <si>
+    <t>20,650,526.3</t>
   </si>
 </sst>
 </file>
@@ -1681,61 +1639,61 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.0824289828856332</v>
+        <v>0.1319439823536859</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="12">
-        <v>0.06562860371981286</v>
+        <v>0.1320001825933934</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1408285995716065</v>
+        <v>0.09218830500465501</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M9" s="16">
-        <v>0.02649931428648135</v>
+        <v>0.03153607982363959</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1318841687461557</v>
+        <v>0.0215050245453084</v>
       </c>
       <c r="Q9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="S9" s="16">
+        <v>0.0206072482993516</v>
+      </c>
+      <c r="T9" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="U9" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="R9" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="S9" s="16">
-        <v>0.02974856967556827</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="U9" s="17" t="s">
-        <v>113</v>
-      </c>
       <c r="V9" s="18">
-        <v>0.05296730633862167</v>
+        <v>0.0416385241103549</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1747,61 +1705,61 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.06160873209992666</v>
+        <v>0.02790636328975732</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.04027744468708194</v>
+        <v>0.06694314465080917</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1204917423273425</v>
+        <v>0.01842194567618064</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02504943388406887</v>
+        <v>0.018280597895233</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1037110241125339</v>
+        <v>0.0209191613799874</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="S10" s="16">
-        <v>0.02432908779610853</v>
+        <v>0.0166579976141285</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="V10" s="18">
-        <v>0.01871634200433274</v>
+        <v>0.02797776823769691</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1813,61 +1771,61 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.04497641092927564</v>
+        <v>0.02324406385487278</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G11" s="12">
-        <v>0.0401613545631139</v>
+        <v>0.03884105508017033</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0.01674716875603751</v>
+      </c>
+      <c r="K11" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="14">
-        <v>0.0962542444698478</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>87</v>
-      </c>
       <c r="L11" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M11" s="16">
-        <v>0.0197632330834421</v>
+        <v>0.01475409956108299</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="O11" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="P11" s="18">
+        <v>0.0196312183813857</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="R11" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="P11" s="18">
-        <v>0.08138127862816513</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="R11" s="15" t="s">
-        <v>107</v>
-      </c>
       <c r="S11" s="16">
-        <v>0.01563929567676114</v>
+        <v>0.01532049222650672</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="V11" s="18">
-        <v>0.016682417762729</v>
+        <v>0.02224140756226527</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1879,61 +1837,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02178196955804568</v>
+        <v>0.01753452567908591</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G12" s="12">
-        <v>0.02341431696116114</v>
+        <v>0.007491123246421535</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J12" s="14">
-        <v>0.03889474672788043</v>
+        <v>0.01585790065791658</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01513573796502275</v>
+        <v>0.009589050617140903</v>
       </c>
       <c r="N12" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="O12" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="P12" s="18">
+        <v>0.01816229173854191</v>
+      </c>
+      <c r="Q12" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="O12" s="17" t="s">
+      <c r="R12" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="P12" s="18">
-        <v>0.01955046973683633</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="R12" s="15" t="s">
-        <v>109</v>
-      </c>
       <c r="S12" s="16">
-        <v>0.01498961769814228</v>
+        <v>0.01510171070543639</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01527695847640639</v>
+        <v>0.01618493079829828</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1945,61 +1903,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01494326452346776</v>
+        <v>0.01738521653372938</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02285587361358678</v>
+        <v>0.004972495056092379</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01810557583888334</v>
+        <v>0.01437391005383169</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01394403629319913</v>
+        <v>0.00862789140917517</v>
       </c>
       <c r="N13" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="O13" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="P13" s="18">
+        <v>0.01656507648042551</v>
+      </c>
+      <c r="Q13" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="O13" s="17" t="s">
+      <c r="R13" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="P13" s="18">
-        <v>0.0185707575937322</v>
-      </c>
-      <c r="Q13" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="R13" s="15" t="s">
-        <v>111</v>
-      </c>
       <c r="S13" s="16">
-        <v>0.01180523611127968</v>
+        <v>0.01397160305977062</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01501291951205672</v>
+        <v>0.01280920683715495</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2010,7 +1968,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2019,7 +1977,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2028,7 +1986,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2037,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2046,7 +2004,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2055,7 +2013,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2064,7 +2022,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2073,566 +2031,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.1100121830924574</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.1683539716450221</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="10">
-        <v>0.1935572811326099</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0.341072404046016</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>137</v>
-      </c>
       <c r="J16" s="14">
-        <v>0.06556991781750708</v>
+        <v>0.05255012941584079</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="L16" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.01727817615909307</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.04096202029924469</v>
+      </c>
+      <c r="Q16" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="M16" s="16">
-        <v>0.6169931319807117</v>
-      </c>
-      <c r="N16" s="17" t="s">
+      <c r="R16" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="S16" s="16">
+        <v>0.0194917917159549</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="U16" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="O16" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0.04437681578672916</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="S16" s="16">
-        <v>0.2407151300571657</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>166</v>
-      </c>
       <c r="V16" s="18">
-        <v>0.2356356796033243</v>
+        <v>0.01998178340839293</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.0211213394351406</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.09475494921694762</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D17" s="10">
-        <v>0.1597676285856262</v>
-      </c>
-      <c r="E17" s="11" t="s">
+      <c r="J17" s="14">
+        <v>0.008678990065543971</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L17" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0.03459675368750405</v>
-      </c>
-      <c r="H17" s="13" t="s">
+      <c r="M17" s="16">
+        <v>0.01682525102144513</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="O17" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="J17" s="14">
-        <v>0.05302450070388671</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="L17" s="15" t="s">
+      <c r="P17" s="18">
+        <v>0.01767348329300761</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="R17" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="M17" s="16">
-        <v>0.06509403280482118</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="O17" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="P17" s="18">
-        <v>0.03073054210080529</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>161</v>
-      </c>
       <c r="S17" s="16">
-        <v>0.09904451461753164</v>
+        <v>0.01602712172800507</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>167</v>
+        <v>65</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="V17" s="18">
-        <v>0.07282366599053272</v>
+        <v>0.01864117879682422</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.02013420427336131</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.08830045665787484</v>
+      </c>
+      <c r="H18" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="I18" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="10">
-        <v>0.02138723896101886</v>
-      </c>
-      <c r="E18" s="11" t="s">
+      <c r="J18" s="14">
+        <v>0.008354394047087764</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.01560614287280553</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="O18" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.01527262183685004</v>
+      </c>
+      <c r="Q18" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G18" s="12">
-        <v>0.02909700210371567</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="J18" s="14">
-        <v>0.02724940668685171</v>
-      </c>
-      <c r="K18" s="15" t="s">
+      <c r="R18" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="L18" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="M18" s="16">
-        <v>0.01500657770084697</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="P18" s="18">
-        <v>0.01891205049742387</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="R18" s="15" t="s">
-        <v>162</v>
-      </c>
       <c r="S18" s="16">
-        <v>0.08251215261541067</v>
+        <v>0.01484601883682418</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>169</v>
+        <v>54</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02215411460469959</v>
+        <v>0.01749342099301833</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.01223947422973267</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.0305727463876329</v>
+      </c>
+      <c r="H19" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="I19" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="10">
-        <v>0.0200079667072661</v>
-      </c>
-      <c r="E19" s="11" t="s">
+      <c r="J19" s="14">
+        <v>0.007508085264486645</v>
+      </c>
+      <c r="K19" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="L19" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="12">
-        <v>0.007544900722968283</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="13" t="s">
+      <c r="M19" s="16">
+        <v>0.01023903126184691</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="O19" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="J19" s="14">
-        <v>0.01555077899721466</v>
-      </c>
-      <c r="K19" s="15" t="s">
+      <c r="P19" s="18">
+        <v>0.01367317560326419</v>
+      </c>
+      <c r="Q19" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="R19" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="L19" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="M19" s="16">
-        <v>0.01074415493013788</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="O19" s="17" t="s">
+      <c r="S19" s="16">
+        <v>0.0121684314416259</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="U19" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="P19" s="18">
-        <v>0.01467638320771041</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="R19" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="S19" s="16">
-        <v>0.05217436993495179</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>171</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.009336775887564564</v>
+        <v>0.01452684850402393</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.01103382041206449</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.02696570941742714</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D20" s="10">
-        <v>0.01721095795746242</v>
-      </c>
-      <c r="E20" s="11" t="s">
+      <c r="J20" s="14">
+        <v>0.0075036254179807</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="L20" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.005633237895918517</v>
-      </c>
-      <c r="H20" s="13" t="s">
+      <c r="M20" s="16">
+        <v>0.00960525599785968</v>
+      </c>
+      <c r="N20" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="O20" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="J20" s="14">
-        <v>0.01419477377657712</v>
-      </c>
-      <c r="K20" s="15" t="s">
+      <c r="P20" s="18">
+        <v>0.01282994559785347</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="R20" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="L20" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="M20" s="16">
-        <v>0.005380980700856365</v>
-      </c>
-      <c r="N20" s="17" t="s">
+      <c r="S20" s="16">
+        <v>0.009688903069639309</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="O20" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.008770926213112486</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.03110562601455747</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>172</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.007946219317734282</v>
+        <v>0.01152663762617893</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2657495533632913</v>
+        <v>0.3059192915638689</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2303535078260273</v>
+        <v>0.2171242060282717</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1417636167631709</v>
+        <v>0.1763793598882306</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D34" s="22">
-        <v>0.08701981643354768</v>
+        <v>0.09418379644808809</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07518306314965956</v>
+        <v>0.06704945044873421</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="D36" s="22">
-        <v>0.06152681285789777</v>
+        <v>0.04119348778434198</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04922227304576299</v>
+        <v>0.0224158665638121</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D38" s="22">
-        <v>0.0253210844579945</v>
+        <v>0.02228439301042123</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01987566885678112</v>
+        <v>0.01851503900576686</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D40" s="22">
-        <v>0.009960685571479803</v>
+        <v>0.01378077145408128</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D41" s="22">
-        <v>0.008666985580646358</v>
+        <v>0.008973130095212757</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D42" s="22">
-        <v>0.007416292703723643</v>
+        <v>0.008584750636420568</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D43" s="22">
-        <v>0.006146957363093501</v>
+        <v>0.002138315649754994</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0009142589112412884</v>
+        <v>0.001166095802209757</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D45" s="22">
-        <v>6.812139165995335E-05</v>
+        <v>0.0002920456207848625</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3011,331 +2969,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1520185601817579</v>
+        <v>0.2204022015932084</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1151747314968904</v>
+        <v>0.2625146703700137</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="J9" s="14">
-        <v>0.3083025796667169</v>
+        <v>0.1788355222767032</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="M9" s="16">
-        <v>0.07033898135667073</v>
+        <v>0.1348164679870278</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="P9" s="18">
-        <v>0.2976052979657682</v>
+        <v>0.147174994373386</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="S9" s="16">
-        <v>0.06412188143560299</v>
+        <v>0.1588177812968219</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="V9" s="18">
-        <v>0.09540831489632447</v>
+        <v>0.1632939233434104</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1382879468453058</v>
+        <v>0.07910342027574667</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="G10" s="12">
-        <v>0.0906537676115811</v>
+        <v>0.05176160341694647</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1701456021089558</v>
+        <v>0.1515882500033533</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="M10" s="16">
-        <v>0.04357033670570815</v>
+        <v>0.09935301601858509</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1643152546988023</v>
+        <v>0.1051015242186642</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="S10" s="16">
-        <v>0.05555391929591566</v>
+        <v>0.1190897727336952</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="V10" s="18">
-        <v>0.08822468566420519</v>
+        <v>0.1369921571148317</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D11" s="10">
-        <v>0.05498263749327316</v>
+        <v>0.07533046662897555</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="G11" s="12">
-        <v>0.06935445286673772</v>
+        <v>0.04066857544197754</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06092669673223602</v>
+        <v>0.06591239302318758</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="M11" s="16">
-        <v>0.03263758960380859</v>
+        <v>0.0902357568642671</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="P11" s="18">
-        <v>0.05215358321554232</v>
+        <v>0.09038487757157929</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="S11" s="16">
-        <v>0.04907562670885956</v>
+        <v>0.1001113249947646</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="V11" s="18">
-        <v>0.08493698490410069</v>
+        <v>0.09316308680986199</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02021454193981409</v>
+        <v>0.05017570469944723</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="G12" s="12">
-        <v>0.04621462097536844</v>
+        <v>0.01816298419339756</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0449272615678187</v>
+        <v>0.060612900778515</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02253344054883679</v>
+        <v>0.04429890217341106</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="P12" s="18">
-        <v>0.03673939037961428</v>
+        <v>0.06691637003434474</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04391999284803691</v>
+        <v>0.05732344610962366</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="V12" s="18">
-        <v>0.07901936662068079</v>
+        <v>0.04940951005810302</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01243936872250289</v>
+        <v>0.02127995371305237</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="G13" s="12">
-        <v>0.04208842629435958</v>
+        <v>0.008144282315587828</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02370759164260705</v>
+        <v>0.02956280603707944</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01596220761127792</v>
+        <v>0.03068678368185019</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="P13" s="18">
-        <v>0.03409950531579105</v>
+        <v>0.03475090598971599</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="S13" s="16">
-        <v>0.03462867920598627</v>
+        <v>0.04365221675559892</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02320930652406999</v>
+        <v>0.03733973286346923</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3346,7 +3304,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3355,7 +3313,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3364,7 +3322,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3373,7 +3331,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3382,7 +3340,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3391,7 +3349,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3400,7 +3358,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3409,331 +3367,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D16" s="10">
-        <v>0.4254469078912756</v>
+        <v>0.2167101973984329</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="G16" s="12">
-        <v>0.343955176458047</v>
+        <v>0.308449309113921</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1313143047646189</v>
+        <v>0.1348710149267028</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="M16" s="16">
-        <v>0.6382938989535466</v>
+        <v>0.146990485057974</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1184043075512512</v>
+        <v>0.1138899506008489</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="S16" s="16">
-        <v>0.2434811400485104</v>
+        <v>0.1180382198637025</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="V16" s="18">
-        <v>0.23715885416156</v>
+        <v>0.1379029122433227</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D17" s="10">
-        <v>0.05310736496027169</v>
+        <v>0.07331450579073348</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="G17" s="12">
-        <v>0.07808405751623228</v>
+        <v>0.1631193511606995</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="J17" s="14">
-        <v>0.05371838586083219</v>
+        <v>0.1304192592106936</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="M17" s="16">
-        <v>0.09257826622362159</v>
+        <v>0.1112746176062292</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="P17" s="18">
-        <v>0.08294573154408269</v>
+        <v>0.098926681298493</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1435063985416687</v>
+        <v>0.1109191465499321</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="V17" s="18">
-        <v>0.08010701152947948</v>
+        <v>0.095766272961509</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D18" s="10">
-        <v>0.03551642348732439</v>
+        <v>0.06509772050673671</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="G18" s="12">
-        <v>0.05244253260959341</v>
+        <v>0.03918657440662547</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="J18" s="14">
-        <v>0.03991092231769758</v>
+        <v>0.06000613170807255</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02528907411093781</v>
+        <v>0.06791558291101017</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07705722905265927</v>
+        <v>0.08141471018894787</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="S18" s="16">
-        <v>0.1202267308773596</v>
+        <v>0.0577776229255984</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="V18" s="18">
-        <v>0.05709317903598443</v>
+        <v>0.09429059183183244</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02193249495452619</v>
+        <v>0.03532103442163136</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="G19" s="12">
-        <v>0.04913834853890216</v>
+        <v>0.02444259835309653</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="J19" s="14">
-        <v>0.0398740607299884</v>
+        <v>0.04435233040577517</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01583711616840588</v>
+        <v>0.06295638006013018</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02395679079599125</v>
+        <v>0.06182282224702795</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="S19" s="16">
-        <v>0.1072708543949909</v>
+        <v>0.04486327848027136</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="V19" s="18">
-        <v>0.05021816435575584</v>
+        <v>0.0460746219528656</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01791918693791416</v>
+        <v>0.02331870627081831</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02028254555025983</v>
+        <v>0.01934176713226446</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="J20" s="14">
-        <v>0.0209015251226785</v>
+        <v>0.02794980173953517</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01007063362869337</v>
+        <v>0.02652649171756709</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="P20" s="18">
-        <v>0.0181965201427944</v>
+        <v>0.03657980594789468</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="S20" s="16">
-        <v>0.0632955986104297</v>
+        <v>0.03818632250084473</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="V20" s="18">
-        <v>0.04098599292821779</v>
+        <v>0.03123035020991103</v>
       </c>
     </row>
   </sheetData>
